--- a/Dishwasher/Grading/2 stage/6-examples/Dishwasher_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Dishwasher/Grading/2 stage/6-examples/Dishwasher_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dishwasher" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dishwasher" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
@@ -5919,11 +5919,11 @@
         </is>
       </c>
       <c r="C2" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Student model uses ProgramRunning as the main composite state but does not have a DishwasherOn composite state that encompasses the entire system including door and washer regions.</t>
+          <t>Represented by state Dishwasher</t>
         </is>
       </c>
       <c r="E2" s="14" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Student model does not have a Door region. Door behavior is modeled through transitions and guards but not as a separate parallel region.</t>
+          <t>Door states not explicitly modeled as a region</t>
         </is>
       </c>
       <c r="E3" s="16" t="n"/>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>No Door region exists in student model so no initial state for door.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E4" s="14" t="n"/>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Door states are not explicitly modeled as separate states in student model.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E5" s="16" t="n"/>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Door state transitions are not explicitly modeled; door behavior is handled through events and guards.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E6" s="14" t="n"/>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Door locking is modeled as an action in Cleaning entry rather than a state transition.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E7" s="16" t="n"/>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Door Open state is not explicitly modeled as a separate state.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E8" s="14" t="n"/>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Door close transition is not explicitly modeled as a state transition.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E9" s="16" t="n"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Door Locked state is not explicitly modeled as a separate state.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E10" s="14" t="n"/>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Door unlocking is modeled as an action in Cleaning exit rather than a state transition.</t>
+          <t>Door region missing</t>
         </is>
       </c>
       <c r="E11" s="16" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Student model has ProcessRegion which serves as the main washer region containing the cleaning and drying logic.</t>
+          <t>Represented by region Operation</t>
         </is>
       </c>
       <c r="E12" s="14" t="n"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">initial state </t>
+          <t>initial state</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>ProcessRegion has an initial state that transitions to Cleaning.</t>
+          <t>Initial state to Setup</t>
         </is>
       </c>
       <c r="E13" s="16" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Student model initializes in SetupDefaultDrying which handles program selection but does not explicitly show r=1 and dT=20 initialization on the initial transition.</t>
+          <t>Initial transition exists but lacks explicit variable initialization</t>
         </is>
       </c>
       <c r="E14" s="14" t="n"/>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Student model has SetupDefaultDrying and SetupExtendedDrying states that serve as idle states for program selection.</t>
+          <t>Represented by Setup state</t>
         </is>
       </c>
       <c r="E15" s="16" t="n"/>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Student model has selectProgram(program) transitions in both SetupDefaultDrying and SetupExtendedDrying states.</t>
+          <t>Represented by selectProgram transition on Setup</t>
         </is>
       </c>
       <c r="E16" s="14" t="n"/>
@@ -6234,11 +6234,11 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Student model uses [programSelected] guard on start transition but does not explicitly show [n&gt;=1] guard on selectProgram transition.</t>
+          <t>Missing guard for program selection</t>
         </is>
       </c>
       <c r="E17" s="16" t="n"/>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Student model has setProgram(program) action which captures setting the program parameter.</t>
+          <t>Represented by setMaxCycles() action</t>
         </is>
       </c>
       <c r="E18" s="14" t="n"/>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Student model has extendDrying and reduceDrying transitions between SetupDefaultDrying and SetupExtendedDrying states.</t>
+          <t>Handled correctly via parallel region DryingTimeSetting</t>
         </is>
       </c>
       <c r="E19" s="16" t="n"/>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Student model uses setDryingTime actions with 20min and 40min parameters to toggle drying time.</t>
+          <t>Handled via transitions in parallel region</t>
         </is>
       </c>
       <c r="E20" s="14" t="n"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Student model has start transitions from SetupDefaultDrying and SetupExtendedDrying to ProgramRunning which contains Cleaning.</t>
+          <t>Represented by start transition from Setup to Running</t>
         </is>
       </c>
       <c r="E21" s="16" t="n"/>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Student model uses [programSelected] guard but does not explicitly check door.isClosed() on start transition.</t>
+          <t>Missing guard checking if door is closed on start</t>
         </is>
       </c>
       <c r="E22" s="14" t="n"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Student model has lockDoor() in Cleaning entry and initializeProgram action which captures initialization.</t>
+          <t>cycles initialized on start and door locked via entry action on WashingPhase</t>
         </is>
       </c>
       <c r="E23" s="16" t="n"/>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Student model has Cleaning composite state with substates WaterIntake Washing and Draining.</t>
+          <t>Represented by WashingPhase</t>
         </is>
       </c>
       <c r="E24" s="14" t="n"/>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Cleaning state has initial state transitioning to WaterIntake.</t>
+          <t>Initial state to WaterIntake</t>
         </is>
       </c>
       <c r="E25" s="16" t="n"/>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Student model has WaterIntake state which corresponds to Intake.</t>
+          <t>Represented by WaterIntake</t>
         </is>
       </c>
       <c r="E26" s="14" t="n"/>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Student model has waterIntakeComplete transition from WaterIntake to Washing.</t>
+          <t>Represented by waterTaken transition</t>
         </is>
       </c>
       <c r="E27" s="16" t="n"/>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Student model has Washing state.</t>
+          <t>Represented by Washing</t>
         </is>
       </c>
       <c r="E28" s="14" t="n"/>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Student model has washTimerElapsed transition from Washing to Draining with 10min timer in entry action.</t>
+          <t>Represented by after 10min transition</t>
         </is>
       </c>
       <c r="E29" s="16" t="n"/>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Student model has Draining state.</t>
+          <t>Represented by Draining</t>
         </is>
       </c>
       <c r="E30" s="14" t="n"/>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[c &lt; r] </t>
+          <t>[c &lt; r]</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Student model has [cyclesRemaining&gt;1] guard which is semantically equivalent to c&lt;r.</t>
+          <t>Represented by [cycles &lt; maxCycles]</t>
         </is>
       </c>
       <c r="E31" s="16" t="n"/>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Student model has waterDrained transition from Draining back to WaterIntake with cyclesRemaining&gt;1 guard.</t>
+          <t>Represented by transition to WaterIntake</t>
         </is>
       </c>
       <c r="E32" s="14" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Student model has decrementCyclesRemaining() action which updates the cycle counter.</t>
+          <t>Represented by cycles++</t>
         </is>
       </c>
       <c r="E33" s="16" t="n"/>
@@ -6659,11 +6659,11 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Student model transitions from Draining to Drying rather than to an explicit end state but this captures the completion of cleaning.</t>
+          <t>Represented by transition to DryingPhase</t>
         </is>
       </c>
       <c r="E34" s="14" t="n"/>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Student model has [cyclesRemaining==1] guard which is semantically equivalent to c&gt;=r.</t>
+          <t>Represented by [cycles == maxCycles]</t>
         </is>
       </c>
       <c r="E35" s="16" t="n"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Student model does not have a history state for Cleaning.</t>
+          <t>Not used due to alternative parallel region approach</t>
         </is>
       </c>
       <c r="E36" s="14" t="n"/>
@@ -6722,11 +6722,11 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Student model has extendDrying and reduceDrying transitions in DryingTimeRegion during ProgramRunning but not from Cleaning to a history state.</t>
+          <t>Handled correctly via parallel region without interrupting cleaning</t>
         </is>
       </c>
       <c r="E37" s="16" t="n"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Student model has setOrExtendDryingTime and setDryingTime actions in DryingTimeRegion transitions.</t>
+          <t>Handled via parallel region transitions</t>
         </is>
       </c>
       <c r="E38" s="14" t="n"/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Student model has waterDrained transition from Draining to Drying when cyclesRemaining==1.</t>
+          <t>Represented by transition from Draining to DryingPhase</t>
         </is>
       </c>
       <c r="E39" s="16" t="n"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Student model has unlockDoor() in Cleaning exit action.</t>
+          <t>Represented by exit action unlockDoor() on WashingPhase</t>
         </is>
       </c>
       <c r="E40" s="14" t="n"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>Student model has Drying composite state.</t>
+          <t>Represented by DryingPhase and Drying states</t>
         </is>
       </c>
       <c r="E41" s="16" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Student model has dryingTimerElapsed transition from HotAirDrying to SetupDefaultDrying with dryingTimer.</t>
+          <t>Represented by after dryingTime transition to Setup</t>
         </is>
       </c>
       <c r="E42" s="14" t="n"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Student model has extendDrying transition in DryingTimeRegion from RunningDefaultDrying to RunningExtendedDrying.</t>
+          <t>Handled via parallel region</t>
         </is>
       </c>
       <c r="E43" s="16" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Student model has setOrExtendDryingTime(40min) action.</t>
+          <t>Handled via parallel region</t>
         </is>
       </c>
       <c r="E44" s="14" t="n"/>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Student model has doorOpened transition from HotAirDrying to DoorOpenSuspended.</t>
+          <t>Represented by doorOpened transition</t>
         </is>
       </c>
       <c r="E45" s="16" t="n"/>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Student model has DoorOpenSuspended state.</t>
+          <t>Represented by DryingSuspended</t>
         </is>
       </c>
       <c r="E46" s="14" t="n"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Student model has doorClosed transition from DoorOpenSuspended to HotAirDrying.</t>
+          <t>Represented by doorClosed transition</t>
         </is>
       </c>
       <c r="E47" s="5" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>Student model has doorOpenTimerElapsed transition from DoorOpenSuspended to SetupDefaultDrying with 5min timer.</t>
+          <t>Represented by after 5min transition to Setup</t>
         </is>
       </c>
       <c r="E48" s="5" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional states.</t>
+          <t>No unnecessary states</t>
         </is>
       </c>
       <c r="E49" s="5" t="n"/>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional transitions.</t>
+          <t>No unnecessary transitions</t>
         </is>
       </c>
       <c r="E50" s="5" t="n"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional guards.</t>
+          <t>No unnecessary guards</t>
         </is>
       </c>
       <c r="E51" s="5" t="n"/>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect additional actions.</t>
+          <t>No unnecessary actions</t>
         </is>
       </c>
       <c r="E52" s="5" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Additional composite states like ProgramRunning are reasonable modeling choices.</t>
+          <t>No unnecessary composite states</t>
         </is>
       </c>
       <c r="E53" s="5" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DryingTimeRegion is a reasonable parallel region for managing drying time adjustments.</t>
+          <t>Parallel region for drying time is a valid alternative modeling choice</t>
         </is>
       </c>
       <c r="E54" s="5" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>No additional history states present.</t>
+          <t>No unnecessary history states</t>
         </is>
       </c>
       <c r="E55" s="5" t="n"/>
@@ -11100,7 +11100,7 @@
     <row r="1" ht="15.75" customHeight="1" s="67">
       <c r="A1" s="68" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="20" t="inlineStr">
@@ -11167,15 +11167,15 @@
         <v/>
       </c>
       <c r="C3" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A3, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D3" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A3, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A3, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E3" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A3, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F3" s="25">
@@ -11203,15 +11203,15 @@
         <v/>
       </c>
       <c r="C4" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A4, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D4" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A4, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A4, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E4" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A4, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F4" s="25">
@@ -11243,15 +11243,15 @@
         <v/>
       </c>
       <c r="C5" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A5, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D5" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A5, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A5, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E5" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A5, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F5" s="25">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -11283,15 +11283,15 @@
         <v/>
       </c>
       <c r="C6" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A6, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D6" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A6, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A6, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E6" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A6, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F6" s="25">
@@ -11318,15 +11318,15 @@
         <v/>
       </c>
       <c r="C7" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A7, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D7" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A7, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A7, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E7" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A7, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F7" s="25">
@@ -11358,15 +11358,15 @@
         <v/>
       </c>
       <c r="C8" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A8, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D8" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A8, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A8, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E8" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A8, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F8" s="25">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -11398,15 +11398,15 @@
         <v/>
       </c>
       <c r="C9" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$48, $A9, 'GPT-5 Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>SUMIF('GPT-5 Generation'!$A$49:$A$55, $A9, 'GPT-5 Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A9, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E9" s="25">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$48, $A9, 'GPT-5 Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F9" s="25">

--- a/Dishwasher/Grading/2 stage/6-examples/Dishwasher_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Dishwasher/Grading/2 stage/6-examples/Dishwasher_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Dishwasher" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gemini 3.1 Pro Grading" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -11167,15 +11167,15 @@
         <v/>
       </c>
       <c r="C3" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D3" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A3, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A3, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E3" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F3" s="25">
@@ -11203,15 +11203,15 @@
         <v/>
       </c>
       <c r="C4" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D4" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A4, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A4, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E4" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F4" s="25">
@@ -11243,15 +11243,15 @@
         <v/>
       </c>
       <c r="C5" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D5" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A5, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A5, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E5" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F5" s="25">
@@ -11283,15 +11283,15 @@
         <v/>
       </c>
       <c r="C6" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D6" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A6, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A6, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E6" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F6" s="25">
@@ -11318,15 +11318,15 @@
         <v/>
       </c>
       <c r="C7" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D7" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A7, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A7, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E7" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F7" s="25">
@@ -11358,15 +11358,15 @@
         <v/>
       </c>
       <c r="C8" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D8" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A8, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A8, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E8" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F8" s="25">
@@ -11398,15 +11398,15 @@
         <v/>
       </c>
       <c r="C9" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$48)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$48)</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$49:$A$55, $A9, 'Gemini 3.1 Pro Generation'!$C$49:$C$55)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$49:$A$55, $A9, 'Gemini 3.1 Pro Grading'!$C$49:$C$55)</f>
         <v/>
       </c>
       <c r="E9" s="25">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$48, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$48,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$48, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$48,0)</f>
         <v/>
       </c>
       <c r="F9" s="25">
